--- a/data/xlsx/sbce_config_wrong.xlsx
+++ b/data/xlsx/sbce_config_wrong.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="154">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -441,9 +441,6 @@
   </si>
   <si>
     <t xml:space="preserve">10.10.48.187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB</t>
   </si>
   <si>
     <t xml:space="preserve">sbce2-a</t>
@@ -505,7 +502,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -529,6 +526,7 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -573,25 +571,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2085,47 +2075,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -2136,18 +2126,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -2158,7 +2148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2169,18 +2159,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -2191,51 +2181,51 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -2246,7 +2236,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -2257,7 +2247,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -2268,7 +2258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -2276,18 +2266,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -2295,7 +2285,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -2306,7 +2296,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -2318,62 +2308,62 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -2384,7 +2374,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -2395,7 +2385,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -2403,7 +2393,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -2414,7 +2404,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
@@ -2422,7 +2412,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -2430,51 +2420,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -2485,7 +2475,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -2496,51 +2486,51 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
@@ -2548,7 +2538,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
@@ -2556,55 +2546,55 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -2727,71 +2717,79 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B50" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>$B$1="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B50" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2805,47 +2803,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -2856,18 +2854,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -2878,7 +2876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2889,18 +2887,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -2911,18 +2909,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2933,29 +2931,29 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -2966,7 +2964,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -2977,7 +2975,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -2988,7 +2986,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -2996,18 +2994,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -3015,7 +3013,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -3026,7 +3024,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -3038,62 +3036,62 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -3104,7 +3102,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -3115,7 +3113,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -3123,7 +3121,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -3134,7 +3132,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
@@ -3142,7 +3140,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -3150,51 +3148,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -3205,7 +3203,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -3216,7 +3214,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
@@ -3224,7 +3222,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
@@ -3232,7 +3230,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
@@ -3240,7 +3238,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
@@ -3248,7 +3246,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
@@ -3256,7 +3254,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
@@ -3264,7 +3262,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
@@ -3272,7 +3270,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
@@ -3280,7 +3278,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
@@ -3288,7 +3286,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
@@ -3296,7 +3294,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
@@ -3415,67 +3413,75 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="14">
+  <dataValidations count="16">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
       <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
       <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
       <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
       <formula1>$B$1="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
-      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3489,47 +3495,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -3540,18 +3546,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3562,7 +3568,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -3573,18 +3579,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -3595,51 +3601,51 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -3650,7 +3656,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -3661,7 +3667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -3672,7 +3678,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -3680,18 +3686,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -3699,7 +3705,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -3710,7 +3716,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -3718,7 +3724,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -3726,7 +3732,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -3734,7 +3740,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
@@ -3742,7 +3748,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -3750,7 +3756,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
@@ -3758,7 +3764,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -3769,7 +3775,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -3780,7 +3786,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -3788,7 +3794,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -3799,18 +3805,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -3818,51 +3824,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -3873,7 +3879,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -3884,121 +3890,121 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -4116,71 +4122,79 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
       <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
       <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
       <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
       <formula1>$B$1="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
-      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4194,47 +4208,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -4245,18 +4259,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4267,7 +4281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -4278,73 +4292,73 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -4355,7 +4369,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -4366,7 +4380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -4377,7 +4391,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -4385,18 +4399,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -4404,7 +4418,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -4415,7 +4429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -4423,7 +4437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -4431,7 +4445,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -4439,7 +4453,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
@@ -4447,7 +4461,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -4455,7 +4469,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
@@ -4463,7 +4477,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -4474,7 +4488,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -4485,7 +4499,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -4493,7 +4507,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -4504,18 +4518,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -4523,51 +4537,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -4578,7 +4592,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -4589,121 +4603,121 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -4821,71 +4835,79 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>$B$1="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4899,47 +4921,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -4950,18 +4972,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4972,95 +4994,95 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>140</v>
+      <c r="B9" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>140</v>
+      <c r="B11" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -5071,7 +5093,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,7 +5104,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -5090,18 +5112,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -5109,7 +5131,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -5120,7 +5142,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -5132,62 +5154,62 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -5198,7 +5220,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -5209,7 +5231,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -5217,7 +5239,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -5228,7 +5250,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
@@ -5236,7 +5258,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -5244,51 +5266,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -5299,7 +5321,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -5310,7 +5332,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
@@ -5318,7 +5340,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
@@ -5326,7 +5348,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
@@ -5334,7 +5356,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
@@ -5342,7 +5364,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
@@ -5350,7 +5372,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
@@ -5358,7 +5380,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
@@ -5366,7 +5388,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
@@ -5374,7 +5396,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
@@ -5382,7 +5404,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
@@ -5390,7 +5412,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
@@ -5509,71 +5531,83 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="18">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>$B$1="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B9 B11" type="textLength">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B9" type="textLength">
       <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5587,47 +5621,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -5638,18 +5672,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -5660,95 +5694,95 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>143</v>
+      <c r="B11" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -5759,7 +5793,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -5770,7 +5804,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -5778,18 +5812,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -5797,7 +5831,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -5808,7 +5842,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -5816,7 +5850,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -5824,7 +5858,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -5832,7 +5866,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
@@ -5840,7 +5874,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -5848,7 +5882,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
@@ -5856,7 +5890,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -5867,7 +5901,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -5878,7 +5912,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -5886,7 +5920,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -5897,18 +5931,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>141</v>
+      <c r="B31" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -5916,51 +5950,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -5971,7 +6005,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -5982,122 +6016,122 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>145</v>
+      <c r="B43" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>146</v>
+      <c r="B44" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>147</v>
+      <c r="B49" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>127</v>
@@ -6214,71 +6248,79 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>$B$1="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6292,47 +6334,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -6343,18 +6385,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -6365,95 +6407,95 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>143</v>
+      <c r="B11" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -6464,7 +6506,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -6475,7 +6517,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -6483,18 +6525,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -6502,7 +6544,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -6513,7 +6555,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -6521,7 +6563,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -6529,7 +6571,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -6537,7 +6579,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
@@ -6545,7 +6587,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -6553,7 +6595,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,7 +6603,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -6572,7 +6614,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -6583,7 +6625,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -6591,7 +6633,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -6602,18 +6644,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>141</v>
+      <c r="B31" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -6621,51 +6663,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -6676,7 +6718,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -6687,122 +6729,122 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>149</v>
+      <c r="B43" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>144</v>
+      <c r="B44" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>147</v>
+      <c r="B49" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>127</v>
@@ -6919,71 +6961,79 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
       <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
       <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
       <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
       <formula1>$B$1="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
-      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6997,47 +7047,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -7048,18 +7098,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -7070,95 +7120,95 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>151</v>
+      <c r="B11" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -7169,7 +7219,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -7180,7 +7230,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>47</v>
       </c>
@@ -7188,18 +7238,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -7207,7 +7257,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -7218,7 +7268,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -7226,7 +7276,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -7234,7 +7284,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -7242,7 +7292,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>64</v>
       </c>
@@ -7250,7 +7300,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -7258,7 +7308,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
@@ -7266,7 +7316,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -7274,10 +7324,10 @@
         <v>73</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -7288,7 +7338,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -7296,7 +7346,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -7307,18 +7357,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>141</v>
+      <c r="B31" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -7326,51 +7376,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -7381,7 +7431,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -7392,51 +7442,51 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>112</v>
       </c>
@@ -7444,7 +7494,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
@@ -7452,56 +7502,56 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>154</v>
+      <c r="B49" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>127</v>
@@ -7618,71 +7668,79 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
       <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
-      <formula1>0</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
       <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B49" type="custom">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B49" type="custom">
       <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
       <formula1>$B$1="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
-      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/data/xlsx/sbce_config_wrong.xlsx
+++ b/data/xlsx/sbce_config_wrong.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="155">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -486,6 +486,9 @@
   </si>
   <si>
     <t xml:space="preserve">Time Zone - Time Zone in which device is located (for example America/Edmonton)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ntpserver</t>
   </si>
   <si>
     <t xml:space="preserve">10.10.48.200</t>
@@ -576,11 +579,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7329,7 +7332,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>76</v>
@@ -7551,7 +7554,7 @@
         <v>125</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>127</v>
